--- a/tools/autojson/levels.xlsx
+++ b/tools/autojson/levels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A\learn\Maa\MaaTOT\tools\autojson\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC82294A-E4EA-4E5A-9F0E-C3A3B4CA1613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA041E2F-384E-4C84-9050-F256760BC0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -73,9 +78,6 @@
     <t>episode_template</t>
   </si>
   <si>
-    <t>海奥森篇</t>
-  </si>
-  <si>
     <t>夏彦</t>
   </si>
   <si>
@@ -210,6 +212,9 @@
   <si>
     <t>剑兰谷篇</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海.森篇</t>
   </si>
 </sst>
 </file>
@@ -566,23 +571,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.06640625" style="1"/>
+    <col min="11" max="11" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,9 +637,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -643,18 +648,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -663,18 +668,18 @@
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="N3" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -683,18 +688,18 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="N4" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -703,18 +708,18 @@
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="N5" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -723,18 +728,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N6" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -743,18 +748,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N7" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -763,18 +768,18 @@
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N8" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -783,18 +788,18 @@
         <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N9" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -803,18 +808,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -823,7 +828,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
@@ -835,9 +840,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -846,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -858,9 +863,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -869,7 +874,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
@@ -881,9 +886,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
@@ -892,18 +897,18 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="N14" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
@@ -912,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -921,9 +926,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
@@ -932,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -941,9 +946,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
@@ -952,18 +957,18 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="N17" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
@@ -972,7 +977,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
@@ -981,9 +986,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
@@ -992,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -1001,9 +1006,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
@@ -1012,18 +1017,18 @@
         <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1">
         <v>4</v>
@@ -1032,18 +1037,18 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N21" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1">
         <v>4</v>
@@ -1052,18 +1057,18 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N22" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>
@@ -1072,18 +1077,18 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1">
         <v>4</v>
@@ -1092,18 +1097,18 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N24" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1">
         <v>5</v>
@@ -1115,18 +1120,18 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P25" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1">
         <v>5</v>
@@ -1138,18 +1143,18 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1">
         <v>5</v>
@@ -1161,18 +1166,18 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1">
         <v>5</v>
@@ -1184,18 +1189,18 @@
         <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1">
         <v>5</v>
@@ -1207,18 +1212,18 @@
         <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1">
         <v>5</v>
@@ -1230,18 +1235,18 @@
         <v>24</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1">
         <v>5</v>
@@ -1253,18 +1258,18 @@
         <v>28</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="P31" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1">
         <v>5</v>
@@ -1276,18 +1281,18 @@
         <v>32</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="P32" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1">
         <v>5</v>
@@ -1299,18 +1304,18 @@
         <v>36</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="P33" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1">
         <v>6</v>
@@ -1322,18 +1327,18 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="P34" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1">
         <v>6</v>
@@ -1345,18 +1350,18 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M35" s="1">
         <v>1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1">
         <v>6</v>
@@ -1368,18 +1373,18 @@
         <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B37" s="1">
         <v>6</v>
@@ -1391,18 +1396,18 @@
         <v>7</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B38" s="1">
         <v>6</v>
@@ -1414,18 +1419,18 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B39" s="1">
         <v>6</v>
@@ -1437,18 +1442,18 @@
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B40" s="1">
         <v>6</v>
@@ -1460,18 +1465,18 @@
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B41" s="1">
         <v>6</v>
@@ -1483,18 +1488,18 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B42" s="1">
         <v>6</v>
@@ -1506,18 +1511,18 @@
         <v>12</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1">
         <v>6</v>
@@ -1529,18 +1534,18 @@
         <v>16</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B44" s="1">
         <v>6</v>
@@ -1552,18 +1557,18 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B45" s="1">
         <v>6</v>
@@ -1575,18 +1580,18 @@
         <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1">
         <v>6</v>
@@ -1598,18 +1603,18 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1">
         <v>7</v>
@@ -1621,18 +1626,18 @@
         <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1">
         <v>7</v>
@@ -1644,18 +1649,18 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B49" s="1">
         <v>7</v>
@@ -1667,18 +1672,18 @@
         <v>9</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J49" s="1">
         <v>1</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1">
         <v>7</v>
@@ -1690,18 +1695,18 @@
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B51" s="1">
         <v>7</v>
@@ -1713,18 +1718,18 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J51" s="1">
         <v>1</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1">
         <v>7</v>
@@ -1736,18 +1741,18 @@
         <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1">
         <v>7</v>
@@ -1759,18 +1764,18 @@
         <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="P53" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1">
         <v>7</v>
@@ -1782,18 +1787,18 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="P54" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1">
         <v>7</v>
@@ -1805,18 +1810,18 @@
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J55" s="1">
         <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B56" s="1">
         <v>7</v>
@@ -1828,18 +1833,18 @@
         <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="P56" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B57" s="1">
         <v>8</v>
@@ -1848,15 +1853,15 @@
         <v>4</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1">
         <v>8</v>
@@ -1865,15 +1870,15 @@
         <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B59" s="1">
         <v>8</v>
@@ -1882,15 +1887,15 @@
         <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B60" s="1">
         <v>9</v>
@@ -1899,15 +1904,15 @@
         <v>4</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B61" s="1">
         <v>9</v>
@@ -1916,15 +1921,15 @@
         <v>8</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B62" s="1">
         <v>9</v>
@@ -1933,15 +1938,15 @@
         <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B63" s="1">
         <v>10</v>
@@ -1950,15 +1955,15 @@
         <v>4</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B64" s="1">
         <v>10</v>
@@ -1967,15 +1972,15 @@
         <v>8</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B65" s="1">
         <v>10</v>
@@ -1984,15 +1989,15 @@
         <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B66" s="1">
         <v>11</v>
@@ -2004,18 +2009,18 @@
         <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="P66" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B67" s="1">
         <v>11</v>
@@ -2027,18 +2032,18 @@
         <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1">
         <v>11</v>
@@ -2050,18 +2055,18 @@
         <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="P68" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B69" s="1">
         <v>11</v>
@@ -2073,18 +2078,18 @@
         <v>16</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P69" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B70" s="1">
         <v>11</v>
@@ -2096,18 +2101,18 @@
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P70" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B71" s="1">
         <v>11</v>
@@ -2119,18 +2124,18 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P71" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P71" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B72" s="1">
         <v>12</v>
@@ -2139,15 +2144,15 @@
         <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1">
         <v>12</v>
@@ -2156,15 +2161,15 @@
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B74" s="1">
         <v>12</v>
@@ -2173,15 +2178,15 @@
         <v>12</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B75" s="1">
         <v>13</v>
@@ -2190,15 +2195,15 @@
         <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B76" s="1">
         <v>13</v>
@@ -2207,15 +2212,15 @@
         <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" s="1">
         <v>13</v>
@@ -2224,15 +2229,15 @@
         <v>12</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B78" s="1">
         <v>14</v>
@@ -2244,18 +2249,18 @@
         <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B79" s="1">
         <v>14</v>
@@ -2267,18 +2272,18 @@
         <v>8</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P79" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P79" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B80" s="1">
         <v>14</v>
@@ -2290,18 +2295,18 @@
         <v>12</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B81" s="1">
         <v>14</v>
@@ -2313,18 +2318,18 @@
         <v>16</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P81" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P81" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B82" s="1">
         <v>14</v>
@@ -2336,18 +2341,18 @@
         <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P82" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P82" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B83" s="1">
         <v>14</v>
@@ -2359,18 +2364,18 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P83" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P83" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B84" s="1">
         <v>15</v>
@@ -2379,15 +2384,15 @@
         <v>4</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B85" s="1">
         <v>15</v>
@@ -2396,15 +2401,15 @@
         <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B86" s="1">
         <v>15</v>
@@ -2413,15 +2418,15 @@
         <v>12</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B87" s="1">
         <v>16</v>
@@ -2430,15 +2435,15 @@
         <v>4</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B88" s="1">
         <v>16</v>
@@ -2447,15 +2452,15 @@
         <v>8</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B89" s="1">
         <v>16</v>
@@ -2464,15 +2469,15 @@
         <v>12</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B90" s="1">
         <v>17</v>
@@ -2484,18 +2489,18 @@
         <v>4</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="P90" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B91" s="1">
         <v>17</v>
@@ -2507,18 +2512,18 @@
         <v>8</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P91" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B92" s="1">
         <v>17</v>
@@ -2530,18 +2535,18 @@
         <v>12</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B93" s="1">
         <v>17</v>
@@ -2553,18 +2558,18 @@
         <v>16</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P93" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P93" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B94" s="1">
         <v>17</v>
@@ -2576,18 +2581,18 @@
         <v>20</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P94" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P94" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B95" s="1">
         <v>17</v>
@@ -2599,18 +2604,18 @@
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P95" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P95" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B96" s="1">
         <v>18</v>
@@ -2622,18 +2627,18 @@
         <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B97" s="1">
         <v>18</v>
@@ -2645,18 +2650,18 @@
         <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B98" s="1">
         <v>18</v>
@@ -2668,18 +2673,18 @@
         <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P98" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P98" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B99" s="1">
         <v>18</v>
@@ -2691,18 +2696,18 @@
         <v>16</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F99" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P99" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P99" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B100" s="1">
         <v>18</v>
@@ -2714,18 +2719,18 @@
         <v>20</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P100" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P100" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B101" s="1">
         <v>18</v>
@@ -2737,13 +2742,13 @@
         <v>24</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P101" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="P101" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
